--- a/Group_Contribution.xlsx
+++ b/Group_Contribution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TUKAI KUMAR GHOSH\Documents\GitHub\streamlit-app-for-IR-assignment-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809D7D83-80FC-460B-A87A-6AD6223D1814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2EAD28-767D-4383-B7CD-237001F5A966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contribution" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>BIRLA INSTITUTE OF TECHNOLOGY &amp; SCIENCE, PILANI - WILP</t>
   </si>
@@ -53,6 +53,15 @@
   </si>
   <si>
     <t>2025MT12086</t>
+  </si>
+  <si>
+    <t>2025MT12019</t>
+  </si>
+  <si>
+    <t>2025MT13002</t>
+  </si>
+  <si>
+    <t>2025MT12077</t>
   </si>
 </sst>
 </file>
@@ -485,28 +494,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
     </row>
-    <row r="4" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -517,8 +526,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
+    <row r="5" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -526,7 +537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -537,8 +548,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
+    <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
@@ -546,8 +559,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4"/>
+    <row r="8" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
